--- a/artfynd/A 56222-2021 artfynd.xlsx
+++ b/artfynd/A 56222-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56222-2021 artfynd.xlsx
+++ b/artfynd/A 56222-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69300353</v>
+        <v>69300348</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535996.1059093819</v>
+        <v>536046</v>
       </c>
       <c r="R2" t="n">
-        <v>6986510.166838665</v>
+        <v>6986498</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +777,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Senvuxen gran # Picea abies</t>
+          <t>1 substratenheter # Hård granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69300348</v>
+        <v>69300350</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536045.8306197423</v>
+        <v>536049</v>
       </c>
       <c r="R3" t="n">
-        <v>6986497.995858474</v>
+        <v>6986540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +897,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # Hård granlåga # Picea abies</t>
+          <t>1 substratenheter # Hård, klen granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69300347</v>
+        <v>69300353</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -985,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536045.8306197423</v>
+        <v>535996</v>
       </c>
       <c r="R4" t="n">
-        <v>6986497.995858474</v>
+        <v>6986510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,19 +983,9 @@
           <t>2017-06-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-06-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1017,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # Picea abies</t>
+          <t>1 substratenheter # Senvuxen gran # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 56222-2021 artfynd.xlsx
+++ b/artfynd/A 56222-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,8 +1047,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69300353</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>